--- a/2й курс/Вышмат/практическая 6.xlsx
+++ b/2й курс/Вышмат/практическая 6.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nazar\Documents\study\2й курс\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/E629AD99FBAD799B/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1EAF59F-14EA-47A6-B7DA-64471334AE72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B834B9B9-81DB-4206-B5B6-3B4E56829448}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{80AB8070-3398-46F8-9A76-950CD0A55D73}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{80AB8070-3398-46F8-9A76-950CD0A55D73}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>x</t>
   </si>
@@ -51,9 +51,6 @@
   </si>
   <si>
     <t xml:space="preserve">асимптота x = 2 </t>
-  </si>
-  <si>
-    <t>y = kx + b</t>
   </si>
 </sst>
 </file>
@@ -717,197 +714,6 @@
             </c:ext>
           </c:extLst>
         </c:ser>
-        <c:ser>
-          <c:idx val="5"/>
-          <c:order val="5"/>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent6"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:dPt>
-            <c:idx val="11"/>
-            <c:marker>
-              <c:symbol val="none"/>
-            </c:marker>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent6"/>
-                </a:solidFill>
-                <a:prstDash val="dash"/>
-                <a:round/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-E68F-4114-A948-099CAF231D18}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Лист1!$A$2:$A$22</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="21"/>
-                <c:pt idx="0">
-                  <c:v>-10</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>-9</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>-8</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>-7</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>-6</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>-5</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>-4</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>-3</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>-2</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>-1</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>10</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Лист1!$F$1:$F$22</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="22"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>0</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="1"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-E68F-4114-A948-099CAF231D18}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
           <c:showVal val="0"/>
@@ -986,7 +792,7 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="1"/>
+        <c:delete val="0"/>
         <c:axPos val="l"/>
         <c:majorGridlines>
           <c:spPr>
@@ -1006,6 +812,39 @@
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
         <c:crossAx val="1473543888"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
@@ -1976,7 +1815,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41E43862-0A49-49A6-9261-1D732E7F0576}">
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="9.140625" style="1"/>
@@ -1985,7 +1824,7 @@
     <col min="5" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1998,11 +1837,8 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>-10</v>
       </c>
@@ -2016,12 +1852,8 @@
       <c r="D2" s="1">
         <v>2</v>
       </c>
-      <c r="F2" s="1">
-        <f>0 *A2 + 0</f>
-        <v>0</v>
-      </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>-9</v>
       </c>
@@ -2035,12 +1867,8 @@
       <c r="D3" s="1">
         <v>2</v>
       </c>
-      <c r="F3" s="1">
-        <f t="shared" ref="F3:F22" si="1">0 *A3 + 0</f>
-        <v>0</v>
-      </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>-8</v>
       </c>
@@ -2054,12 +1882,8 @@
       <c r="D4" s="1">
         <v>2</v>
       </c>
-      <c r="F4" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>-7</v>
       </c>
@@ -2073,12 +1897,8 @@
       <c r="D5" s="1">
         <v>2</v>
       </c>
-      <c r="F5" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>-6</v>
       </c>
@@ -2092,12 +1912,8 @@
       <c r="D6" s="1">
         <v>2</v>
       </c>
-      <c r="F6" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>-5</v>
       </c>
@@ -2111,12 +1927,8 @@
       <c r="D7" s="1">
         <v>2</v>
       </c>
-      <c r="F7" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>-4</v>
       </c>
@@ -2130,12 +1942,8 @@
       <c r="D8" s="1">
         <v>2</v>
       </c>
-      <c r="F8" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>-3</v>
       </c>
@@ -2149,12 +1957,8 @@
       <c r="D9" s="1">
         <v>2</v>
       </c>
-      <c r="F9" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>-2</v>
       </c>
@@ -2168,12 +1972,8 @@
       <c r="D10" s="1">
         <v>2</v>
       </c>
-      <c r="F10" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>-1</v>
       </c>
@@ -2187,12 +1987,8 @@
       <c r="D11" s="1">
         <v>2</v>
       </c>
-      <c r="F11" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>0</v>
       </c>
@@ -2206,12 +2002,8 @@
       <c r="D12" s="1">
         <v>2</v>
       </c>
-      <c r="F12" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>1</v>
       </c>
@@ -2225,12 +2017,8 @@
       <c r="D13" s="1">
         <v>2</v>
       </c>
-      <c r="F13" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>2</v>
       </c>
@@ -2244,12 +2032,8 @@
       <c r="D14" s="1">
         <v>2</v>
       </c>
-      <c r="F14" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>3</v>
       </c>
@@ -2263,12 +2047,8 @@
       <c r="D15" s="1">
         <v>2</v>
       </c>
-      <c r="F15" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>4</v>
       </c>
@@ -2282,12 +2062,8 @@
       <c r="D16" s="1">
         <v>2</v>
       </c>
-      <c r="F16" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>5</v>
       </c>
@@ -2301,12 +2077,8 @@
       <c r="D17" s="1">
         <v>2</v>
       </c>
-      <c r="F17" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>6</v>
       </c>
@@ -2320,12 +2092,8 @@
       <c r="D18" s="1">
         <v>2</v>
       </c>
-      <c r="F18" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>7</v>
       </c>
@@ -2339,12 +2107,8 @@
       <c r="D19" s="1">
         <v>2</v>
       </c>
-      <c r="F19" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>8</v>
       </c>
@@ -2358,12 +2122,8 @@
       <c r="D20" s="1">
         <v>2</v>
       </c>
-      <c r="F20" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>9</v>
       </c>
@@ -2377,12 +2137,8 @@
       <c r="D21" s="1">
         <v>2</v>
       </c>
-      <c r="F21" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>10</v>
       </c>
@@ -2395,10 +2151,6 @@
       </c>
       <c r="D22" s="1">
         <v>2</v>
-      </c>
-      <c r="F22" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
       </c>
     </row>
   </sheetData>
